--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6255,7 +6255,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7410,7 +7410,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8873,7 +8873,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10028,7 +10028,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10105,7 +10105,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10182,7 +10182,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11183,7 +11183,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11337,7 +11337,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11491,7 +11491,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11568,7 +11568,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11645,7 +11645,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -11953,7 +11953,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12184,7 +12184,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12646,7 +12646,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13185,7 +13185,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13262,7 +13262,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13339,7 +13339,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13416,7 +13416,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13493,7 +13493,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13801,7 +13801,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -13955,7 +13955,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14032,7 +14032,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14186,7 +14186,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14263,7 +14263,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14417,7 +14417,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14494,7 +14494,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14571,7 +14571,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14802,7 +14802,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15033,7 +15033,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15418,7 +15418,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15495,7 +15495,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15803,7 +15803,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -15880,7 +15880,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -15957,7 +15957,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16034,7 +16034,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16111,7 +16111,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16188,7 +16188,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16342,7 +16342,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16419,7 +16419,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16496,7 +16496,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16573,7 +16573,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16727,7 +16727,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16804,7 +16804,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -16881,7 +16881,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17112,7 +17112,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17189,7 +17189,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17266,7 +17266,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17574,7 +17574,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17651,7 +17651,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17728,7 +17728,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17805,7 +17805,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -17882,7 +17882,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -17959,7 +17959,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18036,7 +18036,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18113,7 +18113,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18190,7 +18190,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18344,7 +18344,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18421,7 +18421,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18498,7 +18498,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18575,7 +18575,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18652,7 +18652,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -18883,7 +18883,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -18960,7 +18960,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19037,7 +19037,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19268,7 +19268,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19345,7 +19345,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19422,7 +19422,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19499,7 +19499,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19730,7 +19730,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -19961,7 +19961,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20038,7 +20038,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20192,7 +20192,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20500,7 +20500,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20654,7 +20654,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20731,7 +20731,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -20808,7 +20808,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -20962,7 +20962,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21047,7 +21047,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6255,7 +6255,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7410,7 +7410,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8873,7 +8873,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10028,7 +10028,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10105,7 +10105,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10182,7 +10182,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11183,7 +11183,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11337,7 +11337,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11491,7 +11491,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11568,7 +11568,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11645,7 +11645,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -11953,7 +11953,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12184,7 +12184,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12646,7 +12646,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13185,7 +13185,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13262,7 +13262,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13339,7 +13339,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13416,7 +13416,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13493,7 +13493,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13801,7 +13801,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -13955,7 +13955,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14032,7 +14032,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14186,7 +14186,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14263,7 +14263,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14417,7 +14417,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14494,7 +14494,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14571,7 +14571,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14802,7 +14802,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15033,7 +15033,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15418,7 +15418,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15495,7 +15495,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15803,7 +15803,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -15880,7 +15880,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -15957,7 +15957,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16034,7 +16034,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16111,7 +16111,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16188,7 +16188,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16342,7 +16342,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16419,7 +16419,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16496,7 +16496,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16573,7 +16573,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16727,7 +16727,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16804,7 +16804,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -16881,7 +16881,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17112,7 +17112,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17189,7 +17189,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17266,7 +17266,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17574,7 +17574,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17651,7 +17651,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17728,7 +17728,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17805,7 +17805,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -17882,7 +17882,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -17959,7 +17959,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18036,7 +18036,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18113,7 +18113,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18190,7 +18190,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18344,7 +18344,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18421,7 +18421,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18498,7 +18498,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18575,7 +18575,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18652,7 +18652,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -18883,7 +18883,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -18960,7 +18960,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19037,7 +19037,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19268,7 +19268,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19345,7 +19345,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19422,7 +19422,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19499,7 +19499,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19730,7 +19730,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -19961,7 +19961,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20038,7 +20038,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20192,7 +20192,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20500,7 +20500,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20654,7 +20654,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20731,7 +20731,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -20808,7 +20808,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -20962,7 +20962,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21047,7 +21047,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6255,7 +6255,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7410,7 +7410,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8873,7 +8873,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10028,7 +10028,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10105,7 +10105,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10182,7 +10182,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11183,7 +11183,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11337,7 +11337,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11491,7 +11491,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11568,7 +11568,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11645,7 +11645,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -11953,7 +11953,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12184,7 +12184,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12646,7 +12646,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13185,7 +13185,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13262,7 +13262,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13339,7 +13339,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13416,7 +13416,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13493,7 +13493,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13801,7 +13801,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -13955,7 +13955,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14032,7 +14032,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14186,7 +14186,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14263,7 +14263,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14417,7 +14417,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14494,7 +14494,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14571,7 +14571,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14802,7 +14802,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15033,7 +15033,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15418,7 +15418,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15495,7 +15495,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15803,7 +15803,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -15880,7 +15880,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -15957,7 +15957,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16034,7 +16034,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16111,7 +16111,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16188,7 +16188,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16342,7 +16342,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16419,7 +16419,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16496,7 +16496,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16573,7 +16573,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16727,7 +16727,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16804,7 +16804,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -16881,7 +16881,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17112,7 +17112,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17189,7 +17189,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17266,7 +17266,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17574,7 +17574,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17651,7 +17651,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17728,7 +17728,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17805,7 +17805,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -17882,7 +17882,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -17959,7 +17959,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18036,7 +18036,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18113,7 +18113,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18190,7 +18190,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18344,7 +18344,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18421,7 +18421,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18498,7 +18498,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18575,7 +18575,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18652,7 +18652,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -18883,7 +18883,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -18960,7 +18960,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19037,7 +19037,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19268,7 +19268,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19345,7 +19345,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19422,7 +19422,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19499,7 +19499,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19730,7 +19730,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -19961,7 +19961,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20038,7 +20038,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20192,7 +20192,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20500,7 +20500,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20654,7 +20654,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20731,7 +20731,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -20808,7 +20808,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -20962,7 +20962,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21047,7 +21047,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6255,7 +6255,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7410,7 +7410,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8873,7 +8873,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10028,7 +10028,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10105,7 +10105,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10182,7 +10182,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11183,7 +11183,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11337,7 +11337,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11491,7 +11491,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11568,7 +11568,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11645,7 +11645,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -11953,7 +11953,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12184,7 +12184,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12646,7 +12646,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13185,7 +13185,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13262,7 +13262,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13339,7 +13339,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13416,7 +13416,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13493,7 +13493,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13801,7 +13801,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -13955,7 +13955,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14032,7 +14032,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14186,7 +14186,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14263,7 +14263,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14417,7 +14417,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14494,7 +14494,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14571,7 +14571,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14802,7 +14802,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15033,7 +15033,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15418,7 +15418,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15495,7 +15495,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15803,7 +15803,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -15880,7 +15880,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -15957,7 +15957,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16034,7 +16034,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16111,7 +16111,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16188,7 +16188,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16342,7 +16342,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16419,7 +16419,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16496,7 +16496,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16573,7 +16573,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16727,7 +16727,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16804,7 +16804,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -16881,7 +16881,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17112,7 +17112,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17189,7 +17189,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17266,7 +17266,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17574,7 +17574,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17651,7 +17651,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17728,7 +17728,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17805,7 +17805,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -17882,7 +17882,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -17959,7 +17959,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18036,7 +18036,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18113,7 +18113,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18190,7 +18190,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18344,7 +18344,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18421,7 +18421,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18498,7 +18498,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18575,7 +18575,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18652,7 +18652,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -18883,7 +18883,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -18960,7 +18960,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19037,7 +19037,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19268,7 +19268,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19345,7 +19345,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19422,7 +19422,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19499,7 +19499,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19730,7 +19730,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -19961,7 +19961,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20038,7 +20038,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20192,7 +20192,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20500,7 +20500,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20654,7 +20654,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20731,7 +20731,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -20808,7 +20808,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -20962,7 +20962,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21047,7 +21047,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6255,7 +6255,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7410,7 +7410,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8873,7 +8873,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10028,7 +10028,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10105,7 +10105,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10182,7 +10182,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11183,7 +11183,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11337,7 +11337,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11491,7 +11491,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11568,7 +11568,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11645,7 +11645,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -11953,7 +11953,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12184,7 +12184,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12646,7 +12646,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13185,7 +13185,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13262,7 +13262,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13339,7 +13339,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13416,7 +13416,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13493,7 +13493,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13801,7 +13801,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -13955,7 +13955,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14032,7 +14032,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14186,7 +14186,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14263,7 +14263,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14417,7 +14417,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14494,7 +14494,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14571,7 +14571,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14802,7 +14802,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15033,7 +15033,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15418,7 +15418,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15495,7 +15495,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15803,7 +15803,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -15880,7 +15880,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -15957,7 +15957,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16034,7 +16034,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16111,7 +16111,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16188,7 +16188,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16342,7 +16342,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16419,7 +16419,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16496,7 +16496,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16573,7 +16573,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16727,7 +16727,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16804,7 +16804,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -16881,7 +16881,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17112,7 +17112,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17189,7 +17189,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17266,7 +17266,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17574,7 +17574,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17651,7 +17651,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17728,7 +17728,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17805,7 +17805,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -17882,7 +17882,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -17959,7 +17959,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18036,7 +18036,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18113,7 +18113,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18190,7 +18190,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18344,7 +18344,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18421,7 +18421,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18498,7 +18498,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18575,7 +18575,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18652,7 +18652,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -18883,7 +18883,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -18960,7 +18960,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19037,7 +19037,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19268,7 +19268,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19345,7 +19345,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19422,7 +19422,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19499,7 +19499,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19730,7 +19730,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -19961,7 +19961,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20038,7 +20038,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20192,7 +20192,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20500,7 +20500,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20654,7 +20654,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20731,7 +20731,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -20808,7 +20808,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -20962,7 +20962,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21047,7 +21047,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6255,7 +6255,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7410,7 +7410,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8873,7 +8873,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10028,7 +10028,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10105,7 +10105,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10182,7 +10182,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11183,7 +11183,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11337,7 +11337,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11491,7 +11491,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11568,7 +11568,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11645,7 +11645,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -11953,7 +11953,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12184,7 +12184,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12646,7 +12646,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13185,7 +13185,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13262,7 +13262,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13339,7 +13339,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13416,7 +13416,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13493,7 +13493,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13801,7 +13801,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -13955,7 +13955,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14032,7 +14032,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14186,7 +14186,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14263,7 +14263,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14417,7 +14417,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14494,7 +14494,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14571,7 +14571,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14802,7 +14802,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15033,7 +15033,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15418,7 +15418,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15495,7 +15495,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15803,7 +15803,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -15880,7 +15880,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -15957,7 +15957,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16034,7 +16034,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16111,7 +16111,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16188,7 +16188,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16342,7 +16342,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16419,7 +16419,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16496,7 +16496,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16573,7 +16573,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16727,7 +16727,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16804,7 +16804,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -16881,7 +16881,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17112,7 +17112,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17189,7 +17189,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17266,7 +17266,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17574,7 +17574,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17651,7 +17651,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17728,7 +17728,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17805,7 +17805,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -17882,7 +17882,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -17959,7 +17959,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18036,7 +18036,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18113,7 +18113,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18190,7 +18190,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18344,7 +18344,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18421,7 +18421,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18498,7 +18498,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18575,7 +18575,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18652,7 +18652,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -18883,7 +18883,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -18960,7 +18960,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19037,7 +19037,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19268,7 +19268,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19345,7 +19345,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19422,7 +19422,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19499,7 +19499,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19730,7 +19730,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -19961,7 +19961,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20038,7 +20038,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20192,7 +20192,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20500,7 +20500,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20654,7 +20654,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20731,7 +20731,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -20808,7 +20808,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -20962,7 +20962,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21047,7 +21047,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
